--- a/server/src/uploads/excels/414128/exam.1.mini-test1.xlsx
+++ b/server/src/uploads/excels/414128/exam.1.mini-test1.xlsx
@@ -1,10 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
-  <workbookPr/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28227"/>
+  <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Code\Project\toeic_prep\server\src\uploads\excels\414128\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{997017C4-524E-472C-98F9-271368467FD8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView windowHeight="18285"/>
+    <workbookView xWindow="25974" yWindow="-163" windowWidth="26301" windowHeight="14169" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="784" uniqueCount="557">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="772" uniqueCount="557">
   <si>
     <t>number</t>
   </si>
@@ -2110,15 +2116,11 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="5">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="1">
     <numFmt numFmtId="6" formatCode="&quot;$&quot;#,##0_);[Red]\(&quot;$&quot;#,##0\)"/>
-    <numFmt numFmtId="42" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;_);_(@_)"/>
-    <numFmt numFmtId="44" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="176" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
   </numFmts>
-  <fonts count="27">
+  <fonts count="7">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2153,157 +2155,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <b/>
       <sz val="11"/>
       <color theme="1"/>
@@ -2319,7 +2170,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="34">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -2332,194 +2183,8 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="12">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -2562,253 +2227,11 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
-  <cellStyleXfs count="49">
+  <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="176" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="4" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="6" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
@@ -2824,9 +2247,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
@@ -2840,61 +2260,17 @@
       <alignment wrapText="1"/>
     </xf>
   </cellXfs>
-  <cellStyles count="49">
+  <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Comma" xfId="1" builtinId="3"/>
-    <cellStyle name="Currency" xfId="2" builtinId="4"/>
-    <cellStyle name="Percent" xfId="3" builtinId="5"/>
-    <cellStyle name="Comma [0]" xfId="4" builtinId="6"/>
-    <cellStyle name="Currency [0]" xfId="5" builtinId="7"/>
-    <cellStyle name="Hyperlink" xfId="6" builtinId="8"/>
-    <cellStyle name="Followed Hyperlink" xfId="7" builtinId="9"/>
-    <cellStyle name="Note" xfId="8" builtinId="10"/>
-    <cellStyle name="Warning Text" xfId="9" builtinId="11"/>
-    <cellStyle name="Title" xfId="10" builtinId="15"/>
-    <cellStyle name="CExplanatory Text" xfId="11" builtinId="53"/>
-    <cellStyle name="Heading 1" xfId="12" builtinId="16"/>
-    <cellStyle name="Heading 2" xfId="13" builtinId="17"/>
-    <cellStyle name="Heading 3" xfId="14" builtinId="18"/>
-    <cellStyle name="Heading 4" xfId="15" builtinId="19"/>
-    <cellStyle name="Input" xfId="16" builtinId="20"/>
-    <cellStyle name="Output" xfId="17" builtinId="21"/>
-    <cellStyle name="Calculation" xfId="18" builtinId="22"/>
-    <cellStyle name="Check Cell" xfId="19" builtinId="23"/>
-    <cellStyle name="Linked Cell" xfId="20" builtinId="24"/>
-    <cellStyle name="Total" xfId="21" builtinId="25"/>
-    <cellStyle name="Good" xfId="22" builtinId="26"/>
-    <cellStyle name="Bad" xfId="23" builtinId="27"/>
-    <cellStyle name="Neutral" xfId="24" builtinId="28"/>
-    <cellStyle name="Accent1" xfId="25" builtinId="29"/>
-    <cellStyle name="20% - Accent1" xfId="26" builtinId="30"/>
-    <cellStyle name="40% - Accent1" xfId="27" builtinId="31"/>
-    <cellStyle name="60% - Accent1" xfId="28" builtinId="32"/>
-    <cellStyle name="Accent2" xfId="29" builtinId="33"/>
-    <cellStyle name="20% - Accent2" xfId="30" builtinId="34"/>
-    <cellStyle name="40% - Accent2" xfId="31" builtinId="35"/>
-    <cellStyle name="60% - Accent2" xfId="32" builtinId="36"/>
-    <cellStyle name="Accent3" xfId="33" builtinId="37"/>
-    <cellStyle name="20% - Accent3" xfId="34" builtinId="38"/>
-    <cellStyle name="40% - Accent3" xfId="35" builtinId="39"/>
-    <cellStyle name="60% - Accent3" xfId="36" builtinId="40"/>
-    <cellStyle name="Accent4" xfId="37" builtinId="41"/>
-    <cellStyle name="20% - Accent4" xfId="38" builtinId="42"/>
-    <cellStyle name="40% - Accent4" xfId="39" builtinId="43"/>
-    <cellStyle name="60% - Accent4" xfId="40" builtinId="44"/>
-    <cellStyle name="Accent5" xfId="41" builtinId="45"/>
-    <cellStyle name="20% - Accent5" xfId="42" builtinId="46"/>
-    <cellStyle name="40% - Accent5" xfId="43" builtinId="47"/>
-    <cellStyle name="60% - Accent5" xfId="44" builtinId="48"/>
-    <cellStyle name="Accent6" xfId="45" builtinId="49"/>
-    <cellStyle name="20% - Accent6" xfId="46" builtinId="50"/>
-    <cellStyle name="40% - Accent6" xfId="47" builtinId="51"/>
-    <cellStyle name="60% - Accent6" xfId="48" builtinId="52"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -3181,29 +2557,29 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:M101"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.3"/>
   <cols>
-    <col min="2" max="2" width="7.37142857142857" customWidth="1"/>
-    <col min="3" max="3" width="13.3714285714286" customWidth="1"/>
-    <col min="4" max="4" width="12.247619047619" customWidth="1"/>
-    <col min="5" max="5" width="47.6285714285714" customWidth="1"/>
-    <col min="6" max="6" width="16.6285714285714" customWidth="1"/>
-    <col min="7" max="7" width="16.1238095238095" customWidth="1"/>
+    <col min="2" max="2" width="7.375" customWidth="1"/>
+    <col min="3" max="3" width="13.375" customWidth="1"/>
+    <col min="4" max="4" width="12.25" customWidth="1"/>
+    <col min="5" max="5" width="47.625" customWidth="1"/>
+    <col min="6" max="6" width="16.625" customWidth="1"/>
+    <col min="7" max="7" width="16.125" customWidth="1"/>
     <col min="8" max="8" width="17" customWidth="1"/>
-    <col min="9" max="9" width="20.8761904761905" customWidth="1"/>
-    <col min="10" max="10" width="14.247619047619" customWidth="1"/>
-    <col min="12" max="12" width="25.1428571428571" customWidth="1"/>
-    <col min="13" max="13" width="56.7142857142857" customWidth="1"/>
+    <col min="9" max="9" width="20.875" customWidth="1"/>
+    <col min="10" max="10" width="14.25" customWidth="1"/>
+    <col min="12" max="12" width="25.125" customWidth="1"/>
+    <col min="13" max="13" width="56.75" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="15.75" spans="1:13">
+    <row r="1" spans="1:13" ht="16.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -3244,7 +2620,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="2" spans="1:12">
+    <row r="2" spans="1:13">
       <c r="A2" s="1">
         <v>1</v>
       </c>
@@ -3280,7 +2656,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="3" spans="1:12">
+    <row r="3" spans="1:13">
       <c r="A3" s="1">
         <v>2</v>
       </c>
@@ -3314,7 +2690,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="4" spans="1:12">
+    <row r="4" spans="1:13">
       <c r="A4" s="1">
         <v>3</v>
       </c>
@@ -3348,7 +2724,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="5" spans="1:12">
+    <row r="5" spans="1:13">
       <c r="A5" s="1">
         <v>4</v>
       </c>
@@ -3382,7 +2758,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="6" spans="1:12">
+    <row r="6" spans="1:13">
       <c r="A6" s="1">
         <v>5</v>
       </c>
@@ -3414,7 +2790,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="7" spans="1:12">
+    <row r="7" spans="1:13">
       <c r="A7" s="1">
         <v>6</v>
       </c>
@@ -3446,7 +2822,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="8" spans="1:12">
+    <row r="8" spans="1:13">
       <c r="A8" s="1">
         <v>7</v>
       </c>
@@ -3478,7 +2854,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="9" spans="1:12">
+    <row r="9" spans="1:13">
       <c r="A9" s="1">
         <v>8</v>
       </c>
@@ -3510,7 +2886,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="10" spans="1:12">
+    <row r="10" spans="1:13">
       <c r="A10" s="1">
         <v>9</v>
       </c>
@@ -3542,7 +2918,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="11" spans="1:12">
+    <row r="11" spans="1:13">
       <c r="A11" s="1">
         <v>10</v>
       </c>
@@ -3574,7 +2950,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="12" spans="1:12">
+    <row r="12" spans="1:13">
       <c r="A12" s="1">
         <v>11</v>
       </c>
@@ -3606,7 +2982,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="13" spans="1:12">
+    <row r="13" spans="1:13">
       <c r="A13" s="1">
         <v>12</v>
       </c>
@@ -3638,7 +3014,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="14" spans="1:12">
+    <row r="14" spans="1:13">
       <c r="A14" s="1">
         <v>13</v>
       </c>
@@ -3670,7 +3046,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="15" spans="1:12">
+    <row r="15" spans="1:13">
       <c r="A15" s="1">
         <v>14</v>
       </c>
@@ -3702,7 +3078,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="16" ht="409.5" spans="1:13">
+    <row r="16" spans="1:13" ht="171.2">
       <c r="A16" s="1">
         <v>15</v>
       </c>
@@ -3741,7 +3117,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="17" ht="409.5" spans="1:13">
+    <row r="17" spans="1:13" ht="171.2">
       <c r="A17" s="1">
         <v>16</v>
       </c>
@@ -3778,7 +3154,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="18" ht="409.5" spans="1:13">
+    <row r="18" spans="1:13" ht="171.2">
       <c r="A18" s="1">
         <v>17</v>
       </c>
@@ -3815,7 +3191,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="19" ht="409.5" spans="1:13">
+    <row r="19" spans="1:13" ht="228.25">
       <c r="A19" s="1">
         <v>18</v>
       </c>
@@ -3852,7 +3228,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="20" ht="409.5" spans="1:13">
+    <row r="20" spans="1:13" ht="228.25">
       <c r="A20" s="1">
         <v>19</v>
       </c>
@@ -3889,7 +3265,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="21" ht="409.5" spans="1:13">
+    <row r="21" spans="1:13" ht="228.25">
       <c r="A21" s="1">
         <v>20</v>
       </c>
@@ -3926,7 +3302,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="22" ht="409.5" spans="1:13">
+    <row r="22" spans="1:13" ht="185.45">
       <c r="A22" s="1">
         <v>21</v>
       </c>
@@ -3963,7 +3339,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="23" ht="409.5" spans="1:13">
+    <row r="23" spans="1:13" ht="185.45">
       <c r="A23" s="1">
         <v>22</v>
       </c>
@@ -4000,7 +3376,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="24" ht="409.5" spans="1:13">
+    <row r="24" spans="1:13" ht="185.45">
       <c r="A24" s="1">
         <v>23</v>
       </c>
@@ -4037,7 +3413,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="25" ht="409.5" spans="1:13">
+    <row r="25" spans="1:13" ht="171.2">
       <c r="A25" s="1">
         <v>24</v>
       </c>
@@ -4074,7 +3450,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="26" ht="409.5" spans="1:13">
+    <row r="26" spans="1:13" ht="171.2">
       <c r="A26" s="1">
         <v>25</v>
       </c>
@@ -4111,7 +3487,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="27" ht="180" spans="1:13">
+    <row r="27" spans="1:13" ht="171.2">
       <c r="A27" s="1">
         <v>26</v>
       </c>
@@ -4148,7 +3524,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="28" ht="150" spans="1:13">
+    <row r="28" spans="1:13" ht="142.65">
       <c r="A28" s="1">
         <v>27</v>
       </c>
@@ -4181,11 +3557,11 @@
       <c r="L28" s="6" t="s">
         <v>163</v>
       </c>
-      <c r="M28" s="9" t="s">
+      <c r="M28" s="7" t="s">
         <v>164</v>
       </c>
     </row>
-    <row r="29" ht="150" spans="1:13">
+    <row r="29" spans="1:13" ht="142.65">
       <c r="A29" s="1">
         <v>28</v>
       </c>
@@ -4218,11 +3594,11 @@
       <c r="L29" s="6" t="s">
         <v>163</v>
       </c>
-      <c r="M29" s="9" t="s">
+      <c r="M29" s="7" t="s">
         <v>164</v>
       </c>
     </row>
-    <row r="30" ht="150" spans="1:13">
+    <row r="30" spans="1:13" ht="142.65">
       <c r="A30" s="1">
         <v>29</v>
       </c>
@@ -4255,11 +3631,11 @@
       <c r="L30" s="6" t="s">
         <v>163</v>
       </c>
-      <c r="M30" s="9" t="s">
+      <c r="M30" s="7" t="s">
         <v>164</v>
       </c>
     </row>
-    <row r="31" ht="195" spans="1:13">
+    <row r="31" spans="1:13" ht="171.2">
       <c r="A31" s="1">
         <v>30</v>
       </c>
@@ -4292,11 +3668,11 @@
       <c r="L31" s="6" t="s">
         <v>163</v>
       </c>
-      <c r="M31" s="9" t="s">
+      <c r="M31" s="7" t="s">
         <v>181</v>
       </c>
     </row>
-    <row r="32" ht="195" spans="1:13">
+    <row r="32" spans="1:13" ht="171.2">
       <c r="A32" s="1">
         <v>31</v>
       </c>
@@ -4329,11 +3705,11 @@
       <c r="L32" s="6" t="s">
         <v>187</v>
       </c>
-      <c r="M32" s="9" t="s">
+      <c r="M32" s="7" t="s">
         <v>181</v>
       </c>
     </row>
-    <row r="33" ht="195" spans="1:13">
+    <row r="33" spans="1:13" ht="171.2">
       <c r="A33" s="1">
         <v>32</v>
       </c>
@@ -4366,11 +3742,11 @@
       <c r="L33" s="6" t="s">
         <v>187</v>
       </c>
-      <c r="M33" s="9" t="s">
+      <c r="M33" s="7" t="s">
         <v>181</v>
       </c>
     </row>
-    <row r="34" ht="150" spans="1:13">
+    <row r="34" spans="1:13" ht="142.65">
       <c r="A34" s="1">
         <v>33</v>
       </c>
@@ -4378,7 +3754,9 @@
       <c r="C34" s="1" t="s">
         <v>193</v>
       </c>
-      <c r="D34" s="1"/>
+      <c r="D34" s="1" t="s">
+        <v>213</v>
+      </c>
       <c r="E34" s="1" t="s">
         <v>194</v>
       </c>
@@ -4403,18 +3781,16 @@
       <c r="L34" s="6" t="s">
         <v>199</v>
       </c>
-      <c r="M34" s="9" t="s">
+      <c r="M34" s="7" t="s">
         <v>200</v>
       </c>
     </row>
-    <row r="35" ht="150" spans="1:13">
+    <row r="35" spans="1:13" ht="142.65">
       <c r="A35" s="1">
         <v>34</v>
       </c>
       <c r="B35" s="1"/>
-      <c r="C35" s="1" t="s">
-        <v>193</v>
-      </c>
+      <c r="C35" s="1"/>
       <c r="D35" s="1"/>
       <c r="E35" s="1" t="s">
         <v>201</v>
@@ -4440,18 +3816,16 @@
       <c r="L35" s="6" t="s">
         <v>199</v>
       </c>
-      <c r="M35" s="9" t="s">
+      <c r="M35" s="7" t="s">
         <v>200</v>
       </c>
     </row>
-    <row r="36" ht="180" spans="1:13">
+    <row r="36" spans="1:13" ht="171.2">
       <c r="A36" s="1">
         <v>35</v>
       </c>
       <c r="B36" s="1"/>
-      <c r="C36" s="1" t="s">
-        <v>193</v>
-      </c>
+      <c r="C36" s="1"/>
       <c r="D36" s="1"/>
       <c r="E36" s="1" t="s">
         <v>206</v>
@@ -4477,11 +3851,11 @@
       <c r="L36" s="6" t="s">
         <v>199</v>
       </c>
-      <c r="M36" s="9" t="s">
+      <c r="M36" s="7" t="s">
         <v>211</v>
       </c>
     </row>
-    <row r="37" ht="409.5" spans="1:13">
+    <row r="37" spans="1:13" ht="409.6">
       <c r="A37" s="1">
         <v>36</v>
       </c>
@@ -4489,9 +3863,7 @@
       <c r="C37" s="1" t="s">
         <v>212</v>
       </c>
-      <c r="D37" s="1" t="s">
-        <v>213</v>
-      </c>
+      <c r="D37" s="1"/>
       <c r="E37" s="1" t="s">
         <v>214</v>
       </c>
@@ -4516,18 +3888,16 @@
       <c r="L37" s="6" t="s">
         <v>217</v>
       </c>
-      <c r="M37" s="9" t="s">
+      <c r="M37" s="7" t="s">
         <v>218</v>
       </c>
     </row>
-    <row r="38" ht="409.5" spans="1:13">
+    <row r="38" spans="1:13" ht="409.6">
       <c r="A38" s="1">
         <v>37</v>
       </c>
       <c r="B38" s="1"/>
-      <c r="C38" s="1" t="s">
-        <v>212</v>
-      </c>
+      <c r="C38" s="1"/>
       <c r="D38" s="1"/>
       <c r="E38" s="1" t="s">
         <v>219</v>
@@ -4553,18 +3923,16 @@
       <c r="L38" s="6" t="s">
         <v>217</v>
       </c>
-      <c r="M38" s="9" t="s">
+      <c r="M38" s="7" t="s">
         <v>218</v>
       </c>
     </row>
-    <row r="39" ht="409.5" spans="1:13">
+    <row r="39" spans="1:13" ht="409.6">
       <c r="A39" s="1">
         <v>38</v>
       </c>
       <c r="B39" s="1"/>
-      <c r="C39" s="1" t="s">
-        <v>212</v>
-      </c>
+      <c r="C39" s="1"/>
       <c r="D39" s="1"/>
       <c r="E39" s="1" t="s">
         <v>220</v>
@@ -4590,11 +3958,11 @@
       <c r="L39" s="6" t="s">
         <v>217</v>
       </c>
-      <c r="M39" s="9" t="s">
+      <c r="M39" s="7" t="s">
         <v>218</v>
       </c>
     </row>
-    <row r="40" ht="195" spans="1:13">
+    <row r="40" spans="1:13" ht="185.45">
       <c r="A40" s="1">
         <v>39</v>
       </c>
@@ -4627,18 +3995,16 @@
       <c r="L40" s="6" t="s">
         <v>217</v>
       </c>
-      <c r="M40" s="9" t="s">
+      <c r="M40" s="7" t="s">
         <v>231</v>
       </c>
     </row>
-    <row r="41" ht="195" spans="1:13">
+    <row r="41" spans="1:13" ht="185.45">
       <c r="A41" s="1">
         <v>40</v>
       </c>
       <c r="B41" s="1"/>
-      <c r="C41" s="1" t="s">
-        <v>225</v>
-      </c>
+      <c r="C41" s="1"/>
       <c r="D41" s="1"/>
       <c r="E41" s="1" t="s">
         <v>232</v>
@@ -4664,18 +4030,16 @@
       <c r="L41" s="6" t="s">
         <v>237</v>
       </c>
-      <c r="M41" s="9" t="s">
+      <c r="M41" s="7" t="s">
         <v>231</v>
       </c>
     </row>
-    <row r="42" ht="195" spans="1:13">
+    <row r="42" spans="1:13" ht="185.45">
       <c r="A42" s="1">
         <v>41</v>
       </c>
       <c r="B42" s="1"/>
-      <c r="C42" s="1" t="s">
-        <v>225</v>
-      </c>
+      <c r="C42" s="1"/>
       <c r="D42" s="1"/>
       <c r="E42" s="1" t="s">
         <v>238</v>
@@ -4701,11 +4065,11 @@
       <c r="L42" s="6" t="s">
         <v>237</v>
       </c>
-      <c r="M42" s="9" t="s">
+      <c r="M42" s="7" t="s">
         <v>231</v>
       </c>
     </row>
-    <row r="43" ht="300" spans="1:13">
+    <row r="43" spans="1:13" ht="271.05">
       <c r="A43" s="1">
         <v>42</v>
       </c>
@@ -4738,18 +4102,16 @@
       <c r="L43" s="6" t="s">
         <v>249</v>
       </c>
-      <c r="M43" s="9" t="s">
+      <c r="M43" s="7" t="s">
         <v>250</v>
       </c>
     </row>
-    <row r="44" ht="300" spans="1:13">
+    <row r="44" spans="1:13" ht="271.05">
       <c r="A44" s="1">
         <v>43</v>
       </c>
       <c r="B44" s="1"/>
-      <c r="C44" s="1" t="s">
-        <v>243</v>
-      </c>
+      <c r="C44" s="1"/>
       <c r="D44" s="1"/>
       <c r="E44" s="1" t="s">
         <v>251</v>
@@ -4775,18 +4137,16 @@
       <c r="L44" s="6" t="s">
         <v>249</v>
       </c>
-      <c r="M44" s="9" t="s">
+      <c r="M44" s="7" t="s">
         <v>250</v>
       </c>
     </row>
-    <row r="45" ht="285" spans="1:13">
+    <row r="45" spans="1:13" ht="256.75">
       <c r="A45" s="1">
         <v>44</v>
       </c>
       <c r="B45" s="1"/>
-      <c r="C45" s="1" t="s">
-        <v>243</v>
-      </c>
+      <c r="C45" s="1"/>
       <c r="D45" s="1"/>
       <c r="E45" s="1" t="s">
         <v>256</v>
@@ -4812,11 +4172,11 @@
       <c r="L45" s="6" t="s">
         <v>249</v>
       </c>
-      <c r="M45" s="9" t="s">
+      <c r="M45" s="7" t="s">
         <v>261</v>
       </c>
     </row>
-    <row r="46" ht="345" spans="1:13">
+    <row r="46" spans="1:13" ht="313.85000000000002">
       <c r="A46" s="1">
         <v>45</v>
       </c>
@@ -4849,18 +4209,16 @@
       <c r="L46" s="6" t="s">
         <v>249</v>
       </c>
-      <c r="M46" s="9" t="s">
+      <c r="M46" s="7" t="s">
         <v>268</v>
       </c>
     </row>
-    <row r="47" ht="345" spans="1:13">
+    <row r="47" spans="1:13" ht="313.85000000000002">
       <c r="A47" s="1">
         <v>46</v>
       </c>
       <c r="B47" s="1"/>
-      <c r="C47" s="1" t="s">
-        <v>262</v>
-      </c>
+      <c r="C47" s="1"/>
       <c r="D47" s="1"/>
       <c r="E47" s="1" t="s">
         <v>269</v>
@@ -4886,18 +4244,16 @@
       <c r="L47" s="6" t="s">
         <v>274</v>
       </c>
-      <c r="M47" s="9" t="s">
+      <c r="M47" s="7" t="s">
         <v>268</v>
       </c>
     </row>
-    <row r="48" ht="345" spans="1:13">
+    <row r="48" spans="1:13" ht="313.85000000000002">
       <c r="A48" s="1">
         <v>47</v>
       </c>
       <c r="B48" s="1"/>
-      <c r="C48" s="1" t="s">
-        <v>262</v>
-      </c>
+      <c r="C48" s="1"/>
       <c r="D48" s="1"/>
       <c r="E48" s="1" t="s">
         <v>275</v>
@@ -4923,11 +4279,11 @@
       <c r="L48" s="6" t="s">
         <v>274</v>
       </c>
-      <c r="M48" s="9" t="s">
+      <c r="M48" s="7" t="s">
         <v>268</v>
       </c>
     </row>
-    <row r="49" ht="390" spans="1:13">
+    <row r="49" spans="1:13" ht="370.9">
       <c r="A49" s="1">
         <v>48</v>
       </c>
@@ -4960,18 +4316,16 @@
       <c r="L49" s="6" t="s">
         <v>274</v>
       </c>
-      <c r="M49" s="9" t="s">
+      <c r="M49" s="7" t="s">
         <v>286</v>
       </c>
     </row>
-    <row r="50" ht="390" spans="1:13">
+    <row r="50" spans="1:13" ht="370.9">
       <c r="A50" s="1">
         <v>49</v>
       </c>
       <c r="B50" s="1"/>
-      <c r="C50" s="1" t="s">
-        <v>280</v>
-      </c>
+      <c r="C50" s="1"/>
       <c r="D50" s="1"/>
       <c r="E50" s="1" t="s">
         <v>287</v>
@@ -4997,18 +4351,16 @@
       <c r="L50" s="6" t="s">
         <v>274</v>
       </c>
-      <c r="M50" s="9" t="s">
+      <c r="M50" s="7" t="s">
         <v>286</v>
       </c>
     </row>
-    <row r="51" ht="390" spans="1:13">
+    <row r="51" spans="1:13" ht="370.9">
       <c r="A51" s="1">
         <v>50</v>
       </c>
       <c r="B51" s="1"/>
-      <c r="C51" s="1" t="s">
-        <v>280</v>
-      </c>
+      <c r="C51" s="1"/>
       <c r="D51" s="1"/>
       <c r="E51" s="1" t="s">
         <v>292</v>
@@ -5034,11 +4386,11 @@
       <c r="L51" s="6" t="s">
         <v>274</v>
       </c>
-      <c r="M51" s="9" t="s">
+      <c r="M51" s="7" t="s">
         <v>286</v>
       </c>
     </row>
-    <row r="52" spans="1:12">
+    <row r="52" spans="1:13">
       <c r="A52" s="1">
         <v>51</v>
       </c>
@@ -5072,7 +4424,7 @@
         <v>303</v>
       </c>
     </row>
-    <row r="53" spans="1:12">
+    <row r="53" spans="1:13">
       <c r="A53" s="1">
         <v>52</v>
       </c>
@@ -5104,7 +4456,7 @@
         <v>303</v>
       </c>
     </row>
-    <row r="54" spans="1:12">
+    <row r="54" spans="1:13">
       <c r="A54" s="1">
         <v>53</v>
       </c>
@@ -5136,7 +4488,7 @@
         <v>303</v>
       </c>
     </row>
-    <row r="55" spans="1:12">
+    <row r="55" spans="1:13">
       <c r="A55" s="1">
         <v>54</v>
       </c>
@@ -5168,7 +4520,7 @@
         <v>303</v>
       </c>
     </row>
-    <row r="56" spans="1:12">
+    <row r="56" spans="1:13">
       <c r="A56" s="1">
         <v>55</v>
       </c>
@@ -5200,7 +4552,7 @@
         <v>323</v>
       </c>
     </row>
-    <row r="57" spans="1:12">
+    <row r="57" spans="1:13">
       <c r="A57" s="1">
         <v>56</v>
       </c>
@@ -5232,7 +4584,7 @@
         <v>323</v>
       </c>
     </row>
-    <row r="58" spans="1:12">
+    <row r="58" spans="1:13">
       <c r="A58" s="1">
         <v>57</v>
       </c>
@@ -5264,7 +4616,7 @@
         <v>334</v>
       </c>
     </row>
-    <row r="59" spans="1:12">
+    <row r="59" spans="1:13">
       <c r="A59" s="1">
         <v>58</v>
       </c>
@@ -5296,7 +4648,7 @@
         <v>334</v>
       </c>
     </row>
-    <row r="60" spans="1:12">
+    <row r="60" spans="1:13">
       <c r="A60" s="1">
         <v>59</v>
       </c>
@@ -5328,7 +4680,7 @@
         <v>334</v>
       </c>
     </row>
-    <row r="61" spans="1:12">
+    <row r="61" spans="1:13">
       <c r="A61" s="1">
         <v>60</v>
       </c>
@@ -5360,7 +4712,7 @@
         <v>350</v>
       </c>
     </row>
-    <row r="62" spans="1:12">
+    <row r="62" spans="1:13">
       <c r="A62" s="1">
         <v>61</v>
       </c>
@@ -5392,7 +4744,7 @@
         <v>323</v>
       </c>
     </row>
-    <row r="63" spans="1:12">
+    <row r="63" spans="1:13">
       <c r="A63" s="1">
         <v>62</v>
       </c>
@@ -5424,7 +4776,7 @@
         <v>350</v>
       </c>
     </row>
-    <row r="64" spans="1:12">
+    <row r="64" spans="1:13">
       <c r="A64" s="1">
         <v>63</v>
       </c>
@@ -5488,13 +4840,13 @@
         <v>366</v>
       </c>
     </row>
-    <row r="66" ht="104.95" customHeight="1" spans="1:12">
+    <row r="66" spans="1:12" ht="104.95" customHeight="1">
       <c r="A66" s="1">
         <v>65</v>
       </c>
       <c r="B66" s="1"/>
       <c r="C66" s="1"/>
-      <c r="D66" s="10" t="s">
+      <c r="D66" s="9" t="s">
         <v>372</v>
       </c>
       <c r="E66" s="1" t="s">
@@ -5582,13 +4934,13 @@
         <v>387</v>
       </c>
     </row>
-    <row r="69" ht="123.8" customHeight="1" spans="1:12">
+    <row r="69" spans="1:12" ht="123.8" customHeight="1">
       <c r="A69" s="1">
         <v>68</v>
       </c>
       <c r="B69" s="1"/>
       <c r="C69" s="1"/>
-      <c r="D69" s="10" t="s">
+      <c r="D69" s="9" t="s">
         <v>388</v>
       </c>
       <c r="E69" s="1"/>
@@ -5674,13 +5026,13 @@
         <v>378</v>
       </c>
     </row>
-    <row r="72" ht="131.3" customHeight="1" spans="1:12">
+    <row r="72" spans="1:12" ht="131.30000000000001" customHeight="1">
       <c r="A72" s="1">
         <v>71</v>
       </c>
       <c r="B72" s="1"/>
       <c r="C72" s="1"/>
-      <c r="D72" s="10" t="s">
+      <c r="D72" s="9" t="s">
         <v>403</v>
       </c>
       <c r="E72" s="1"/>
@@ -5766,31 +5118,31 @@
         <v>393</v>
       </c>
     </row>
-    <row r="75" ht="97.5" customHeight="1" spans="1:12">
-      <c r="A75" s="11">
+    <row r="75" spans="1:12" ht="97.5" customHeight="1">
+      <c r="A75" s="10">
         <v>74</v>
       </c>
-      <c r="B75" s="11"/>
-      <c r="C75" s="11"/>
-      <c r="D75" s="12" t="s">
+      <c r="B75" s="10"/>
+      <c r="C75" s="10"/>
+      <c r="D75" s="11" t="s">
         <v>414</v>
       </c>
-      <c r="E75" s="11" t="s">
+      <c r="E75" s="10" t="s">
         <v>415</v>
       </c>
-      <c r="F75" s="11" t="s">
+      <c r="F75" s="10" t="s">
         <v>416</v>
       </c>
-      <c r="G75" s="11" t="s">
+      <c r="G75" s="10" t="s">
         <v>417</v>
       </c>
-      <c r="H75" s="11" t="s">
+      <c r="H75" s="10" t="s">
         <v>418</v>
       </c>
-      <c r="I75" s="11" t="s">
+      <c r="I75" s="10" t="s">
         <v>419</v>
       </c>
-      <c r="J75" s="11" t="s">
+      <c r="J75" s="10" t="s">
         <v>33</v>
       </c>
       <c r="K75">
@@ -5928,31 +5280,31 @@
         <v>439</v>
       </c>
     </row>
-    <row r="80" ht="102.1" customHeight="1" spans="1:12">
-      <c r="A80" s="11">
+    <row r="80" spans="1:12" ht="102.1" customHeight="1">
+      <c r="A80" s="10">
         <v>79</v>
       </c>
-      <c r="B80" s="11"/>
-      <c r="C80" s="11"/>
-      <c r="D80" s="12" t="s">
+      <c r="B80" s="10"/>
+      <c r="C80" s="10"/>
+      <c r="D80" s="11" t="s">
         <v>440</v>
       </c>
-      <c r="E80" s="11" t="s">
+      <c r="E80" s="10" t="s">
         <v>441</v>
       </c>
-      <c r="F80" s="11" t="s">
+      <c r="F80" s="10" t="s">
         <v>442</v>
       </c>
-      <c r="G80" s="11" t="s">
+      <c r="G80" s="10" t="s">
         <v>443</v>
       </c>
-      <c r="H80" s="11" t="s">
+      <c r="H80" s="10" t="s">
         <v>444</v>
       </c>
-      <c r="I80" s="11" t="s">
+      <c r="I80" s="10" t="s">
         <v>445</v>
       </c>
-      <c r="J80" s="11" t="s">
+      <c r="J80" s="10" t="s">
         <v>19</v>
       </c>
       <c r="K80">
@@ -6036,16 +5388,16 @@
       <c r="E83" s="1" t="s">
         <v>457</v>
       </c>
-      <c r="F83" s="13" t="s">
+      <c r="F83" s="12" t="s">
         <v>458</v>
       </c>
-      <c r="G83" s="13" t="s">
+      <c r="G83" s="12" t="s">
         <v>459</v>
       </c>
-      <c r="H83" s="13" t="s">
+      <c r="H83" s="12" t="s">
         <v>460</v>
       </c>
-      <c r="I83" s="13" t="s">
+      <c r="I83" s="12" t="s">
         <v>461</v>
       </c>
       <c r="J83" s="1" t="s">
@@ -6090,31 +5442,31 @@
         <v>420</v>
       </c>
     </row>
-    <row r="85" ht="99.7" customHeight="1" spans="1:12">
-      <c r="A85" s="14">
+    <row r="85" spans="1:12" ht="99.7" customHeight="1">
+      <c r="A85" s="13">
         <v>84</v>
       </c>
-      <c r="B85" s="14"/>
-      <c r="C85" s="14"/>
-      <c r="D85" s="15" t="s">
+      <c r="B85" s="13"/>
+      <c r="C85" s="13"/>
+      <c r="D85" s="14" t="s">
         <v>467</v>
       </c>
-      <c r="E85" s="14" t="s">
+      <c r="E85" s="13" t="s">
         <v>468</v>
       </c>
-      <c r="F85" s="14" t="s">
+      <c r="F85" s="13" t="s">
         <v>469</v>
       </c>
-      <c r="G85" s="14" t="s">
+      <c r="G85" s="13" t="s">
         <v>470</v>
       </c>
-      <c r="H85" s="14" t="s">
+      <c r="H85" s="13" t="s">
         <v>471</v>
       </c>
-      <c r="I85" s="14" t="s">
+      <c r="I85" s="13" t="s">
         <v>472</v>
       </c>
-      <c r="J85" s="14" t="s">
+      <c r="J85" s="13" t="s">
         <v>33</v>
       </c>
       <c r="K85">
@@ -6252,31 +5604,31 @@
         <v>432</v>
       </c>
     </row>
-    <row r="90" ht="93.75" customHeight="1" spans="1:12">
-      <c r="A90" s="11">
+    <row r="90" spans="1:12" ht="93.75" customHeight="1">
+      <c r="A90" s="10">
         <v>89</v>
       </c>
-      <c r="B90" s="11"/>
-      <c r="C90" s="11"/>
-      <c r="D90" s="12" t="s">
+      <c r="B90" s="10"/>
+      <c r="C90" s="10"/>
+      <c r="D90" s="11" t="s">
         <v>492</v>
       </c>
-      <c r="E90" s="11" t="s">
+      <c r="E90" s="10" t="s">
         <v>493</v>
       </c>
-      <c r="F90" s="11" t="s">
+      <c r="F90" s="10" t="s">
         <v>494</v>
       </c>
-      <c r="G90" s="11" t="s">
+      <c r="G90" s="10" t="s">
         <v>495</v>
       </c>
-      <c r="H90" s="11" t="s">
+      <c r="H90" s="10" t="s">
         <v>496</v>
       </c>
-      <c r="I90" s="11" t="s">
+      <c r="I90" s="10" t="s">
         <v>497</v>
       </c>
-      <c r="J90" s="11" t="s">
+      <c r="J90" s="10" t="s">
         <v>19</v>
       </c>
       <c r="K90">
@@ -6350,31 +5702,31 @@
         <v>432</v>
       </c>
     </row>
-    <row r="93" ht="72.7" customHeight="1" spans="1:12">
-      <c r="A93" s="11">
+    <row r="93" spans="1:12" ht="72.7" customHeight="1">
+      <c r="A93" s="10">
         <v>92</v>
       </c>
-      <c r="B93" s="11"/>
-      <c r="C93" s="11"/>
-      <c r="D93" s="12" t="s">
+      <c r="B93" s="10"/>
+      <c r="C93" s="10"/>
+      <c r="D93" s="11" t="s">
         <v>508</v>
       </c>
-      <c r="E93" s="11" t="s">
+      <c r="E93" s="10" t="s">
         <v>509</v>
       </c>
-      <c r="F93" s="11" t="s">
+      <c r="F93" s="10" t="s">
         <v>510</v>
       </c>
-      <c r="G93" s="11" t="s">
+      <c r="G93" s="10" t="s">
         <v>511</v>
       </c>
-      <c r="H93" s="11" t="s">
+      <c r="H93" s="10" t="s">
         <v>512</v>
       </c>
-      <c r="I93" s="11" t="s">
+      <c r="I93" s="10" t="s">
         <v>513</v>
       </c>
-      <c r="J93" s="11" t="s">
+      <c r="J93" s="10" t="s">
         <v>47</v>
       </c>
       <c r="K93">
@@ -6394,16 +5746,16 @@
       <c r="E94" s="1" t="s">
         <v>514</v>
       </c>
-      <c r="F94" s="13" t="s">
+      <c r="F94" s="12" t="s">
         <v>515</v>
       </c>
-      <c r="G94" s="13" t="s">
+      <c r="G94" s="12" t="s">
         <v>516</v>
       </c>
-      <c r="H94" s="13" t="s">
+      <c r="H94" s="12" t="s">
         <v>517</v>
       </c>
-      <c r="I94" s="13" t="s">
+      <c r="I94" s="12" t="s">
         <v>518</v>
       </c>
       <c r="J94" s="1" t="s">
@@ -6416,31 +5768,31 @@
         <v>439</v>
       </c>
     </row>
-    <row r="95" ht="99.7" customHeight="1" spans="1:12">
-      <c r="A95" s="11">
+    <row r="95" spans="1:12" ht="99.7" customHeight="1">
+      <c r="A95" s="10">
         <v>94</v>
       </c>
-      <c r="B95" s="11"/>
-      <c r="C95" s="11"/>
-      <c r="D95" s="12" t="s">
+      <c r="B95" s="10"/>
+      <c r="C95" s="10"/>
+      <c r="D95" s="11" t="s">
         <v>519</v>
       </c>
-      <c r="E95" s="11" t="s">
+      <c r="E95" s="10" t="s">
         <v>520</v>
       </c>
-      <c r="F95" s="11" t="s">
+      <c r="F95" s="10" t="s">
         <v>521</v>
       </c>
-      <c r="G95" s="11" t="s">
+      <c r="G95" s="10" t="s">
         <v>522</v>
       </c>
-      <c r="H95" s="11" t="s">
+      <c r="H95" s="10" t="s">
         <v>523</v>
       </c>
-      <c r="I95" s="11" t="s">
+      <c r="I95" s="10" t="s">
         <v>524</v>
       </c>
-      <c r="J95" s="11" t="s">
+      <c r="J95" s="10" t="s">
         <v>47</v>
       </c>
       <c r="K95">
@@ -6514,31 +5866,31 @@
         <v>439</v>
       </c>
     </row>
-    <row r="98" ht="86.3" customHeight="1" spans="1:12">
-      <c r="A98" s="11">
+    <row r="98" spans="1:12" ht="86.3" customHeight="1">
+      <c r="A98" s="10">
         <v>97</v>
       </c>
-      <c r="B98" s="11"/>
-      <c r="C98" s="11"/>
-      <c r="D98" s="12" t="s">
+      <c r="B98" s="10"/>
+      <c r="C98" s="10"/>
+      <c r="D98" s="11" t="s">
         <v>535</v>
       </c>
-      <c r="E98" s="11" t="s">
+      <c r="E98" s="10" t="s">
         <v>536</v>
       </c>
-      <c r="F98" s="11" t="s">
+      <c r="F98" s="10" t="s">
         <v>537</v>
       </c>
-      <c r="G98" s="11" t="s">
+      <c r="G98" s="10" t="s">
         <v>538</v>
       </c>
-      <c r="H98" s="11" t="s">
+      <c r="H98" s="10" t="s">
         <v>539</v>
       </c>
-      <c r="I98" s="11" t="s">
+      <c r="I98" s="10" t="s">
         <v>540</v>
       </c>
-      <c r="J98" s="11" t="s">
+      <c r="J98" s="10" t="s">
         <v>19</v>
       </c>
       <c r="K98">
@@ -6580,31 +5932,31 @@
         <v>446</v>
       </c>
     </row>
-    <row r="100" ht="107.35" customHeight="1" spans="1:12">
-      <c r="A100" s="11">
+    <row r="100" spans="1:12" ht="107.35" customHeight="1">
+      <c r="A100" s="10">
         <v>99</v>
       </c>
-      <c r="B100" s="11"/>
-      <c r="C100" s="11"/>
-      <c r="D100" s="12" t="s">
+      <c r="B100" s="10"/>
+      <c r="C100" s="10"/>
+      <c r="D100" s="11" t="s">
         <v>546</v>
       </c>
-      <c r="E100" s="11" t="s">
+      <c r="E100" s="10" t="s">
         <v>547</v>
       </c>
-      <c r="F100" s="11" t="s">
+      <c r="F100" s="10" t="s">
         <v>548</v>
       </c>
-      <c r="G100" s="11" t="s">
+      <c r="G100" s="10" t="s">
         <v>549</v>
       </c>
-      <c r="H100" s="11" t="s">
+      <c r="H100" s="10" t="s">
         <v>550</v>
       </c>
-      <c r="I100" s="11" t="s">
+      <c r="I100" s="10" t="s">
         <v>551</v>
       </c>
-      <c r="J100" s="11" t="s">
+      <c r="J100" s="10" t="s">
         <v>19</v>
       </c>
       <c r="K100">
@@ -6624,16 +5976,16 @@
       <c r="E101" s="1" t="s">
         <v>552</v>
       </c>
-      <c r="F101" s="13" t="s">
+      <c r="F101" s="12" t="s">
         <v>553</v>
       </c>
-      <c r="G101" s="13" t="s">
+      <c r="G101" s="12" t="s">
         <v>554</v>
       </c>
-      <c r="H101" s="13" t="s">
+      <c r="H101" s="12" t="s">
         <v>555</v>
       </c>
-      <c r="I101" s="13" t="s">
+      <c r="I101" s="12" t="s">
         <v>556</v>
       </c>
       <c r="J101" s="1" t="s">
@@ -6648,6 +6000,5 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <headerFooter/>
 </worksheet>
 </file>